--- a/artfynd/A 37948-2024 artfynd.xlsx
+++ b/artfynd/A 37948-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125681550</v>
+        <v>125681445</v>
       </c>
       <c r="B2" t="n">
-        <v>79033</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>82779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392547</v>
+        <v>392597</v>
       </c>
       <c r="R2" t="n">
-        <v>6705047</v>
+        <v>6705020</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Liten förekomst på gammal björk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,49 +775,36 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125681518</v>
+        <v>125681550</v>
       </c>
       <c r="B3" t="n">
-        <v>78979</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -876,7 +853,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Senvuxen gran.</t>
+          <t>Liten förekomst på gammal björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125681445</v>
+        <v>125681508</v>
       </c>
       <c r="B4" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +891,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392597</v>
+        <v>392573</v>
       </c>
       <c r="R4" t="n">
-        <v>6705020</v>
+        <v>6705029</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125681508</v>
+        <v>125681518</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,25 +991,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1051,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392573</v>
+        <v>392547</v>
       </c>
       <c r="R5" t="n">
-        <v>6705029</v>
+        <v>6705047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Senvuxen gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37948-2024 artfynd.xlsx
+++ b/artfynd/A 37948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681445</v>
       </c>
       <c r="B2" t="n">
-        <v>82779</v>
+        <v>82780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125681550</v>
       </c>
       <c r="B3" t="n">
-        <v>79053</v>
+        <v>79054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>125681508</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>125681518</v>
       </c>
       <c r="B5" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37948-2024 artfynd.xlsx
+++ b/artfynd/A 37948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681445</v>
       </c>
       <c r="B2" t="n">
-        <v>82780</v>
+        <v>82784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125681550</v>
       </c>
       <c r="B3" t="n">
-        <v>79054</v>
+        <v>79058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>125681508</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>125681518</v>
       </c>
       <c r="B5" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37948-2024 artfynd.xlsx
+++ b/artfynd/A 37948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681445</v>
       </c>
       <c r="B2" t="n">
-        <v>82784</v>
+        <v>82785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125681550</v>
       </c>
       <c r="B3" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>125681508</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>125681518</v>
       </c>
       <c r="B5" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37948-2024 artfynd.xlsx
+++ b/artfynd/A 37948-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681445</v>
       </c>
       <c r="B2" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>125681550</v>
       </c>
       <c r="B3" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>125681508</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>125681518</v>
       </c>
       <c r="B5" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37948-2024 artfynd.xlsx
+++ b/artfynd/A 37948-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125681445</v>
+        <v>125681518</v>
       </c>
       <c r="B2" t="n">
-        <v>82789</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,25 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -713,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392597</v>
+        <v>392547</v>
       </c>
       <c r="R2" t="n">
-        <v>6705020</v>
+        <v>6705047</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,6 +757,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Senvuxen gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,36 +788,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125681550</v>
+        <v>125681558</v>
       </c>
       <c r="B3" t="n">
-        <v>79063</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -813,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392547</v>
+        <v>392531</v>
       </c>
       <c r="R3" t="n">
-        <v>6705047</v>
+        <v>6705049</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Liten förekomst på gammal björk.</t>
+          <t>Senvuxen gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125681508</v>
+        <v>125681445</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -891,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392573</v>
+        <v>392597</v>
       </c>
       <c r="R4" t="n">
-        <v>6705029</v>
+        <v>6705020</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,37 +1001,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125681518</v>
+        <v>125681419</v>
       </c>
       <c r="B5" t="n">
-        <v>79009</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1026,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392547</v>
+        <v>392580</v>
       </c>
       <c r="R5" t="n">
-        <v>6705047</v>
+        <v>6705007</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1087,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Senvuxen gran.</t>
+          <t>I gammal gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,6 +1111,416 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125681438</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NV Lundbergsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>392590</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6705013</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt i senvuxen gran.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125681508</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NV Lundbergsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>392573</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6705029</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125681559</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NV Lundbergsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>392531</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6705049</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125681550</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NV Lundbergsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>392547</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6705047</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Liten förekomst på gammal björk.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37948-2024 artfynd.xlsx
+++ b/artfynd/A 37948-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681518</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681445</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681419</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681438</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681508</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681559</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,8 +1561,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681550</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>